--- a/sample_documents/VDD_STG_STD_PaymentIntegrity_TPL_CAQH_To_DL_Ingestion_1005034.xlsx
+++ b/sample_documents/VDD_STG_STD_PaymentIntegrity_TPL_CAQH_To_DL_Ingestion_1005034.xlsx
@@ -7,9 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FILES" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="caqh" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FILES" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="caqh" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -480,96 +479,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="108" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="46" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Vendor Data Dictionary</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>DERIVED WORKED EXAMPLE — VDD_STG_STD_PaymentIntegrity_TPL_CAQH_To_DL_Ingestion_1005034</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="46" customHeight="1">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>PROVENANCE — READ THIS</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Generated by scripts/build_vdd_from_sttm.py from the SOURCE band of STTM_STG_STD_PaymentIntegrity_TPL_CAQH_To_DL_Ingestion_1005034.xlsx. It is NOT the vendor's specification: it is a transcription of what analysts had already written down. Treat it as a worked example of a filled-in dictionary, never as evidence of what the vendor actually sends.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="46" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Do not use it to score a run</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>It is circular: a dictionary derived from an STTM must never be used to evaluate a run against that same STTM, because the source side would be grounded in the answer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="46" customHeight="1">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>What it contains</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>FILES: one row per file the vendor delivers. Then one sheet per file, one row per source column: position, name, data type, length, description, segment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="46" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>What it deliberately does NOT contain</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Anything the CLIENT decides — target catalog, schema, table, column names, datatypes, load strategy. Those come from the FRD and the standards contracts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="46" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>NOT RECOVERABLE from this STTM</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Example Value, PHI/PII, Required — blank on every field, because the source band does not record them. This is the gap, not a defect of the generator: those facts exist only in the vendor's spec. The agent will report them as missing and gate the affected cells rather than guess.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:S2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -773,7 +682,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
